--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for the Observation school period.</t>
+    <t>ValueSet pour l'Observation de la Période Scolaire.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/ValueSet-tddui-observation-periode-scolaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
